--- a/master-db/ford.xlsx
+++ b/master-db/ford.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kang1\Desktop\db 완료전\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kang1\Documents\GitHub\ildeung-battery-v1\master-db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04C77459-1E3C-42B1-A1E5-D36C4279F83F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC20EA42-BF53-44C2-8D07-20FF04920232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="58">
   <si>
     <t>제조사</t>
   </si>
@@ -53,9 +53,6 @@
   </si>
   <si>
     <t/>
-  </si>
-  <si>
-    <t>대기</t>
   </si>
   <si>
     <t>디젤 2000cc</t>
@@ -199,6 +196,10 @@
   </si>
   <si>
     <t>디젤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>완료</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -607,25 +608,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
         <v>14</v>
       </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" t="s">
-        <v>15</v>
-      </c>
       <c r="F2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G2" t="s">
         <v>10</v>
       </c>
-      <c r="H2" t="s">
-        <v>11</v>
+      <c r="H2" s="1" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -633,25 +634,25 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
         <v>16</v>
       </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>17</v>
-      </c>
       <c r="F3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G3" t="s">
         <v>10</v>
       </c>
-      <c r="H3" t="s">
-        <v>11</v>
+      <c r="H3" s="1" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -659,25 +660,25 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
         <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G4" t="s">
         <v>10</v>
       </c>
-      <c r="H4" t="s">
-        <v>11</v>
+      <c r="H4" s="1" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -685,25 +686,25 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
         <v>19</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>20</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>21</v>
       </c>
-      <c r="E5" t="s">
-        <v>22</v>
-      </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G5" t="s">
         <v>10</v>
       </c>
-      <c r="H5" t="s">
-        <v>11</v>
+      <c r="H5" s="1" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -711,25 +712,25 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
         <v>19</v>
       </c>
-      <c r="C6" t="s">
-        <v>20</v>
-      </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G6" t="s">
         <v>10</v>
       </c>
-      <c r="H6" t="s">
-        <v>11</v>
+      <c r="H6" s="1" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -737,25 +738,25 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
         <v>9</v>
       </c>
       <c r="E7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G7" t="s">
         <v>10</v>
       </c>
-      <c r="H7" t="s">
-        <v>11</v>
+      <c r="H7" s="1" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -763,25 +764,25 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
         <v>25</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
         <v>26</v>
       </c>
-      <c r="D8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" t="s">
-        <v>27</v>
-      </c>
       <c r="F8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G8" t="s">
         <v>10</v>
       </c>
-      <c r="H8" t="s">
-        <v>11</v>
+      <c r="H8" s="1" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -789,25 +790,25 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
         <v>28</v>
       </c>
-      <c r="D9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" t="s">
-        <v>29</v>
-      </c>
       <c r="F9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G9" t="s">
         <v>10</v>
       </c>
-      <c r="H9" t="s">
-        <v>11</v>
+      <c r="H9" s="1" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -815,25 +816,25 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D10" t="s">
         <v>9</v>
       </c>
       <c r="E10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G10" t="s">
         <v>10</v>
       </c>
-      <c r="H10" t="s">
-        <v>11</v>
+      <c r="H10" s="1" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -841,25 +842,25 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" t="s">
         <v>30</v>
       </c>
-      <c r="D11" t="s">
-        <v>31</v>
-      </c>
       <c r="E11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G11" t="s">
         <v>10</v>
       </c>
-      <c r="H11" t="s">
-        <v>11</v>
+      <c r="H11" s="1" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -867,25 +868,25 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" t="s">
         <v>32</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>33</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>34</v>
       </c>
-      <c r="E12" t="s">
-        <v>35</v>
-      </c>
       <c r="F12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G12" t="s">
         <v>10</v>
       </c>
-      <c r="H12" t="s">
-        <v>11</v>
+      <c r="H12" s="1" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -893,25 +894,25 @@
         <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G13" t="s">
         <v>10</v>
       </c>
-      <c r="H13" t="s">
-        <v>11</v>
+      <c r="H13" s="1" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -919,25 +920,25 @@
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" t="s">
         <v>36</v>
       </c>
-      <c r="D14" t="s">
-        <v>37</v>
-      </c>
       <c r="E14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G14" t="s">
         <v>10</v>
       </c>
-      <c r="H14" t="s">
-        <v>11</v>
+      <c r="H14" s="1" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -945,25 +946,25 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" t="s">
         <v>41</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
+        <v>33</v>
+      </c>
+      <c r="E15" t="s">
         <v>42</v>
       </c>
-      <c r="D15" t="s">
-        <v>34</v>
-      </c>
-      <c r="E15" t="s">
-        <v>43</v>
-      </c>
       <c r="F15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G15" t="s">
-        <v>55</v>
-      </c>
-      <c r="H15" t="s">
-        <v>11</v>
+        <v>54</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -971,25 +972,25 @@
         <v>8</v>
       </c>
       <c r="B16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" t="s">
         <v>41</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E16" t="s">
         <v>42</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E16" t="s">
-        <v>43</v>
-      </c>
       <c r="F16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G16" t="s">
-        <v>55</v>
-      </c>
-      <c r="H16" t="s">
-        <v>11</v>
+        <v>54</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -997,25 +998,25 @@
         <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D17" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" t="s">
         <v>40</v>
       </c>
-      <c r="E17" t="s">
-        <v>41</v>
-      </c>
       <c r="F17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G17" t="s">
         <v>10</v>
       </c>
-      <c r="H17" t="s">
-        <v>11</v>
+      <c r="H17" s="1" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -1023,25 +1024,25 @@
         <v>8</v>
       </c>
       <c r="B18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" t="s">
         <v>45</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
+        <v>47</v>
+      </c>
+      <c r="E18" t="s">
         <v>46</v>
       </c>
-      <c r="D18" t="s">
-        <v>48</v>
-      </c>
-      <c r="E18" t="s">
-        <v>47</v>
-      </c>
       <c r="F18" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G18" t="s">
         <v>10</v>
       </c>
-      <c r="H18" t="s">
-        <v>11</v>
+      <c r="H18" s="1" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -1049,25 +1050,25 @@
         <v>8</v>
       </c>
       <c r="B19" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" t="s">
         <v>49</v>
       </c>
-      <c r="C19" t="s">
-        <v>50</v>
-      </c>
       <c r="D19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G19" t="s">
         <v>10</v>
       </c>
-      <c r="H19" t="s">
-        <v>11</v>
+      <c r="H19" s="1" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -1075,25 +1076,25 @@
         <v>8</v>
       </c>
       <c r="B20" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" t="s">
         <v>49</v>
       </c>
-      <c r="C20" t="s">
-        <v>50</v>
-      </c>
       <c r="D20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G20" t="s">
         <v>10</v>
       </c>
-      <c r="H20" t="s">
-        <v>11</v>
+      <c r="H20" s="1" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -1101,25 +1102,25 @@
         <v>8</v>
       </c>
       <c r="B21" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" t="s">
         <v>49</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>50</v>
       </c>
-      <c r="D21" t="s">
-        <v>51</v>
-      </c>
       <c r="E21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G21" t="s">
         <v>10</v>
       </c>
-      <c r="H21" t="s">
-        <v>11</v>
+      <c r="H21" s="1" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
